--- a/NIFTY_200_Technical_Metrics.xlsx
+++ b/NIFTY_200_Technical_Metrics.xlsx
@@ -2092,7 +2092,7 @@
         <v>58</v>
       </c>
       <c r="P2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Q2">
         <v>1068.56</v>
@@ -2324,7 +2324,7 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="Q4">
         <v>346.55</v>
@@ -2556,7 +2556,7 @@
         <v>91</v>
       </c>
       <c r="P6">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q6">
         <v>2941.23</v>
@@ -2672,7 +2672,7 @@
         <v>96</v>
       </c>
       <c r="P7">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q7">
         <v>1489.64</v>
@@ -2788,7 +2788,7 @@
         <v>87</v>
       </c>
       <c r="P8">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q8">
         <v>1804.44</v>
@@ -2904,7 +2904,7 @@
         <v>98</v>
       </c>
       <c r="P9">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q9">
         <v>222.23</v>
@@ -3020,7 +3020,7 @@
         <v>51</v>
       </c>
       <c r="P10">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q10">
         <v>5322.2</v>
@@ -3136,7 +3136,7 @@
         <v>14</v>
       </c>
       <c r="P11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q11">
         <v>412.43</v>
@@ -3252,7 +3252,7 @@
         <v>29</v>
       </c>
       <c r="P12">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q12">
         <v>1792.16</v>
@@ -3368,7 +3368,7 @@
         <v>79</v>
       </c>
       <c r="P13">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="Q13">
         <v>8472.4</v>
@@ -3484,7 +3484,7 @@
         <v>61</v>
       </c>
       <c r="P14">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q14">
         <v>143.48</v>
@@ -3600,7 +3600,7 @@
         <v>85</v>
       </c>
       <c r="P15">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q15">
         <v>2704.14</v>
@@ -3716,7 +3716,7 @@
         <v>28</v>
       </c>
       <c r="P16">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Q16">
         <v>1507.5</v>
@@ -3832,7 +3832,7 @@
         <v>83</v>
       </c>
       <c r="P17">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q17">
         <v>731.6799999999999</v>
@@ -3948,7 +3948,7 @@
         <v>83</v>
       </c>
       <c r="P18">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18">
         <v>975.08</v>
@@ -4064,7 +4064,7 @@
         <v>80</v>
       </c>
       <c r="P19">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q19">
         <v>1458.26</v>
@@ -4180,7 +4180,7 @@
         <v>69</v>
       </c>
       <c r="P20">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q20">
         <v>1309.72</v>
@@ -4412,7 +4412,7 @@
         <v>21</v>
       </c>
       <c r="P22">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q22">
         <v>1673.22</v>
@@ -4528,7 +4528,7 @@
         <v>17</v>
       </c>
       <c r="P23">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q23">
         <v>10036</v>
@@ -4644,7 +4644,7 @@
         <v>47</v>
       </c>
       <c r="P24">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q24">
         <v>886.1900000000001</v>
@@ -4760,7 +4760,7 @@
         <v>63</v>
       </c>
       <c r="P25">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Q25">
         <v>268.93</v>
@@ -4876,7 +4876,7 @@
         <v>66</v>
       </c>
       <c r="P26">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q26">
         <v>143.94</v>
@@ -5224,7 +5224,7 @@
         <v>87</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q29">
         <v>1931.14</v>
@@ -5340,7 +5340,7 @@
         <v>44</v>
       </c>
       <c r="P30">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="Q30">
         <v>1798.52</v>
@@ -5456,7 +5456,7 @@
         <v>95</v>
       </c>
       <c r="P31">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q31">
         <v>381.91</v>
@@ -5572,7 +5572,7 @@
         <v>75</v>
       </c>
       <c r="P32">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q32">
         <v>415.03</v>
@@ -5688,7 +5688,7 @@
         <v>24</v>
       </c>
       <c r="P33">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q33">
         <v>1569.06</v>
@@ -5804,7 +5804,7 @@
         <v>86</v>
       </c>
       <c r="P34">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="Q34">
         <v>37769</v>
@@ -5920,7 +5920,7 @@
         <v>40</v>
       </c>
       <c r="P35">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q35">
         <v>290.19</v>
@@ -6036,7 +6036,7 @@
         <v>22</v>
       </c>
       <c r="P36">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q36">
         <v>5127.1</v>
@@ -6152,7 +6152,7 @@
         <v>93</v>
       </c>
       <c r="P37">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q37">
         <v>3954.4</v>
@@ -6268,7 +6268,7 @@
         <v>65</v>
       </c>
       <c r="P38">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q38">
         <v>129.8</v>
@@ -6384,7 +6384,7 @@
         <v>91</v>
       </c>
       <c r="P39">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q39">
         <v>907.7</v>
@@ -6500,7 +6500,7 @@
         <v>42</v>
       </c>
       <c r="P40">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q40">
         <v>1489.4</v>
@@ -6616,7 +6616,7 @@
         <v>45</v>
       </c>
       <c r="P41">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q41">
         <v>1382.82</v>
@@ -6848,7 +6848,7 @@
         <v>5</v>
       </c>
       <c r="P43">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q43">
         <v>1412.92</v>
@@ -6964,7 +6964,7 @@
         <v>53</v>
       </c>
       <c r="P44">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q44">
         <v>1399.36</v>
@@ -7080,7 +7080,7 @@
         <v>30</v>
       </c>
       <c r="P45">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q45">
         <v>2038.56</v>
@@ -7196,7 +7196,7 @@
         <v>9</v>
       </c>
       <c r="P46">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q46">
         <v>446.85</v>
@@ -7312,7 +7312,7 @@
         <v>21</v>
       </c>
       <c r="P47">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q47">
         <v>1844.24</v>
@@ -7428,7 +7428,7 @@
         <v>94</v>
       </c>
       <c r="P48">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="Q48">
         <v>5604.8</v>
@@ -7544,7 +7544,7 @@
         <v>20</v>
       </c>
       <c r="P49">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q49">
         <v>424.38</v>
@@ -7660,7 +7660,7 @@
         <v>51</v>
       </c>
       <c r="P50">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q50">
         <v>6641.2</v>
@@ -7776,7 +7776,7 @@
         <v>31</v>
       </c>
       <c r="P51">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="Q51">
         <v>11481.4</v>
@@ -7892,7 +7892,7 @@
         <v>17</v>
       </c>
       <c r="P52">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Q52">
         <v>569.9400000000001</v>
@@ -8008,7 +8008,7 @@
         <v>37</v>
       </c>
       <c r="P53">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q53">
         <v>4035.86</v>
@@ -8124,7 +8124,7 @@
         <v>36</v>
       </c>
       <c r="P54">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q54">
         <v>1273.44</v>
@@ -8240,7 +8240,7 @@
         <v>81</v>
       </c>
       <c r="P55">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q55">
         <v>7192.8</v>
@@ -8466,7 +8466,7 @@
         <v>53</v>
       </c>
       <c r="P57">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q57">
         <v>242.55</v>
@@ -8814,7 +8814,7 @@
         <v>82</v>
       </c>
       <c r="P60">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q60">
         <v>989.4400000000001</v>
@@ -8930,7 +8930,7 @@
         <v>57</v>
       </c>
       <c r="P61">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q61">
         <v>168.16</v>
@@ -9046,7 +9046,7 @@
         <v>73</v>
       </c>
       <c r="P62">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q62">
         <v>2169.76</v>
@@ -9162,7 +9162,7 @@
         <v>78</v>
       </c>
       <c r="P63">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q63">
         <v>101.52</v>
@@ -9278,7 +9278,7 @@
         <v>32</v>
       </c>
       <c r="P64">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Q64">
         <v>2235.18</v>
@@ -9394,7 +9394,7 @@
         <v>26</v>
       </c>
       <c r="P65">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q65">
         <v>1016</v>
@@ -9510,7 +9510,7 @@
         <v>16</v>
       </c>
       <c r="P66">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="Q66">
         <v>1657.96</v>
@@ -9626,7 +9626,7 @@
         <v>79</v>
       </c>
       <c r="P67">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q67">
         <v>3082.36</v>
@@ -9840,7 +9840,7 @@
         <v>98</v>
       </c>
       <c r="P69">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="Q69">
         <v>4843.7</v>
@@ -10072,7 +10072,7 @@
         <v>7</v>
       </c>
       <c r="P71">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q71">
         <v>1145.88</v>
@@ -10188,7 +10188,7 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q72">
         <v>1129.9</v>
@@ -10304,7 +10304,7 @@
         <v>40</v>
       </c>
       <c r="P73">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q73">
         <v>2449.96</v>
@@ -10420,7 +10420,7 @@
         <v>19</v>
       </c>
       <c r="P74">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q74">
         <v>748.1799999999999</v>
@@ -10536,7 +10536,7 @@
         <v>6</v>
       </c>
       <c r="P75">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q75">
         <v>555.0599999999999</v>
@@ -10768,7 +10768,7 @@
         <v>90</v>
       </c>
       <c r="P77">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q77">
         <v>1044.86</v>
@@ -10884,7 +10884,7 @@
         <v>48</v>
       </c>
       <c r="P78">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q78">
         <v>376.75</v>
@@ -11000,7 +11000,7 @@
         <v>33</v>
       </c>
       <c r="P79">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q79">
         <v>2144.2</v>
@@ -11116,7 +11116,7 @@
         <v>47</v>
       </c>
       <c r="P80">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q80">
         <v>554.42</v>
@@ -11232,7 +11232,7 @@
         <v>44</v>
       </c>
       <c r="P81">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="Q81">
         <v>205.53</v>
@@ -11348,7 +11348,7 @@
         <v>55</v>
       </c>
       <c r="P82">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q82">
         <v>1922.9</v>
@@ -11794,7 +11794,7 @@
         <v>99</v>
       </c>
       <c r="P86">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q86">
         <v>14.3</v>
@@ -11910,7 +11910,7 @@
         <v>72</v>
       </c>
       <c r="P87">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q87">
         <v>73.51000000000001</v>
@@ -12026,7 +12026,7 @@
         <v>46</v>
       </c>
       <c r="P88">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q88">
         <v>663.99</v>
@@ -12258,7 +12258,7 @@
         <v>41</v>
       </c>
       <c r="P90">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q90">
         <v>4526.86</v>
@@ -12374,7 +12374,7 @@
         <v>63</v>
       </c>
       <c r="P91">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q91">
         <v>901.62</v>
@@ -12490,7 +12490,7 @@
         <v>50</v>
       </c>
       <c r="P92">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q92">
         <v>418.58</v>
@@ -12606,7 +12606,7 @@
         <v>13</v>
       </c>
       <c r="P93">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q93">
         <v>1138.81</v>
@@ -12722,7 +12722,7 @@
         <v>39</v>
       </c>
       <c r="P94">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="Q94">
         <v>137.16</v>
@@ -12838,7 +12838,7 @@
         <v>11</v>
       </c>
       <c r="P95">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Q95">
         <v>517.74</v>
@@ -13070,7 +13070,7 @@
         <v>10</v>
       </c>
       <c r="P97">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q97">
         <v>94.95</v>
@@ -13186,7 +13186,7 @@
         <v>12</v>
       </c>
       <c r="P98">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q98">
         <v>282.12</v>
@@ -13302,7 +13302,7 @@
         <v>58</v>
       </c>
       <c r="P99">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="Q99">
         <v>1139.42</v>
@@ -13534,7 +13534,7 @@
         <v>71</v>
       </c>
       <c r="P101">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="Q101">
         <v>562.72</v>
@@ -13650,7 +13650,7 @@
         <v>80</v>
       </c>
       <c r="P102">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q102">
         <v>1274.42</v>
@@ -13766,7 +13766,7 @@
         <v>3</v>
       </c>
       <c r="P103">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q103">
         <v>419.08</v>
@@ -13882,7 +13882,7 @@
         <v>4</v>
       </c>
       <c r="P104">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q104">
         <v>344.7</v>
@@ -13998,7 +13998,7 @@
         <v>92</v>
       </c>
       <c r="P105">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q105">
         <v>5229.3</v>
@@ -14114,7 +14114,7 @@
         <v>49</v>
       </c>
       <c r="P106">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q106">
         <v>388.71</v>
@@ -14658,7 +14658,7 @@
         <v>49</v>
       </c>
       <c r="P111">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q111">
         <v>546.03</v>
@@ -14890,7 +14890,7 @@
         <v>65</v>
       </c>
       <c r="P113">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q113">
         <v>3920.98</v>
@@ -15006,7 +15006,7 @@
         <v>84</v>
       </c>
       <c r="P114">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q114">
         <v>264.09</v>
@@ -15122,7 +15122,7 @@
         <v>13</v>
       </c>
       <c r="P115">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Q115">
         <v>3918.26</v>
@@ -15238,7 +15238,7 @@
         <v>62</v>
       </c>
       <c r="P116">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q116">
         <v>2266.5</v>
@@ -15354,7 +15354,7 @@
         <v>37</v>
       </c>
       <c r="P117">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="Q117">
         <v>2990.48</v>
@@ -15470,7 +15470,7 @@
         <v>27</v>
       </c>
       <c r="P118">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q118">
         <v>281.95</v>
@@ -15586,7 +15586,7 @@
         <v>55</v>
       </c>
       <c r="P119">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q119">
         <v>2375.68</v>
@@ -15702,7 +15702,7 @@
         <v>71</v>
       </c>
       <c r="P120">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q120">
         <v>814.39</v>
@@ -15934,7 +15934,7 @@
         <v>25</v>
       </c>
       <c r="P122">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="Q122">
         <v>1008.54</v>
@@ -16050,7 +16050,7 @@
         <v>16</v>
       </c>
       <c r="P123">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q123">
         <v>2389.9</v>
@@ -16166,7 +16166,7 @@
         <v>93</v>
       </c>
       <c r="P124">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Q124">
         <v>2804.84</v>
@@ -16282,7 +16282,7 @@
         <v>38</v>
       </c>
       <c r="P125">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q125">
         <v>1582.2</v>
@@ -16514,7 +16514,7 @@
         <v>74</v>
       </c>
       <c r="P127">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q127">
         <v>849.3</v>
@@ -16630,7 +16630,7 @@
         <v>42</v>
       </c>
       <c r="P128">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="Q128">
         <v>2304.12</v>
@@ -16746,7 +16746,7 @@
         <v>27</v>
       </c>
       <c r="P129">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q129">
         <v>123323</v>
@@ -16862,7 +16862,7 @@
         <v>59</v>
       </c>
       <c r="P130">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q130">
         <v>2957.36</v>
@@ -16978,7 +16978,7 @@
         <v>95</v>
       </c>
       <c r="P131">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q131">
         <v>377.14</v>
@@ -17094,7 +17094,7 @@
         <v>15</v>
       </c>
       <c r="P132">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q132">
         <v>977.8099999999999</v>
@@ -17210,7 +17210,7 @@
         <v>70</v>
       </c>
       <c r="P133">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q133">
         <v>1409.16</v>
@@ -17326,7 +17326,7 @@
         <v>24</v>
       </c>
       <c r="P134">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q134">
         <v>73.22</v>
@@ -17442,7 +17442,7 @@
         <v>82</v>
       </c>
       <c r="P135">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q135">
         <v>89.5</v>
@@ -17558,7 +17558,7 @@
         <v>41</v>
       </c>
       <c r="P136">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q136">
         <v>355.09</v>
@@ -18022,7 +18022,7 @@
         <v>20</v>
       </c>
       <c r="P140">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="Q140">
         <v>446.29</v>
@@ -18254,7 +18254,7 @@
         <v>59</v>
       </c>
       <c r="P142">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="Q142">
         <v>38355</v>
@@ -18370,7 +18370,7 @@
         <v>8</v>
       </c>
       <c r="P143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q143">
         <v>421.25</v>
@@ -18602,7 +18602,7 @@
         <v>30</v>
       </c>
       <c r="P145">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Q145">
         <v>4939.2</v>
@@ -18718,7 +18718,7 @@
         <v>50</v>
       </c>
       <c r="P146">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="Q146">
         <v>425.98</v>
@@ -18834,7 +18834,7 @@
         <v>67</v>
       </c>
       <c r="P147">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q147">
         <v>1750.34</v>
@@ -18950,7 +18950,7 @@
         <v>60</v>
       </c>
       <c r="P148">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q148">
         <v>1496.48</v>
@@ -19066,7 +19066,7 @@
         <v>11</v>
       </c>
       <c r="P149">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q149">
         <v>2799.56</v>
@@ -19182,7 +19182,7 @@
         <v>45</v>
       </c>
       <c r="P150">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q150">
         <v>104.69</v>
@@ -19298,7 +19298,7 @@
         <v>28</v>
       </c>
       <c r="P151">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q151">
         <v>1514.16</v>
@@ -19414,7 +19414,7 @@
         <v>94</v>
       </c>
       <c r="P152">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q152">
         <v>9512</v>
@@ -19530,7 +19530,7 @@
         <v>33</v>
       </c>
       <c r="P153">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q153">
         <v>286.93</v>
@@ -19646,7 +19646,7 @@
         <v>97</v>
       </c>
       <c r="P154">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q154">
         <v>34092</v>
@@ -19762,7 +19762,7 @@
         <v>76</v>
       </c>
       <c r="P155">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q155">
         <v>1067.14</v>
@@ -19878,7 +19878,7 @@
         <v>34</v>
       </c>
       <c r="P156">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q156">
         <v>1344.44</v>
@@ -19994,7 +19994,7 @@
         <v>89</v>
       </c>
       <c r="P157">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q157">
         <v>3490.86</v>
@@ -20110,7 +20110,7 @@
         <v>35</v>
       </c>
       <c r="P158">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q158">
         <v>345.84</v>
@@ -20226,7 +20226,7 @@
         <v>25</v>
       </c>
       <c r="P159">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q159">
         <v>1269.46</v>
@@ -20458,7 +20458,7 @@
         <v>88</v>
       </c>
       <c r="P161">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="Q161">
         <v>183.39</v>
@@ -20574,7 +20574,7 @@
         <v>3</v>
       </c>
       <c r="P162">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q162">
         <v>579.58</v>
@@ -20690,7 +20690,7 @@
         <v>23</v>
       </c>
       <c r="P163">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q163">
         <v>1737.46</v>
@@ -20922,7 +20922,7 @@
         <v>26</v>
       </c>
       <c r="P165">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q165">
         <v>23735</v>
@@ -21154,7 +21154,7 @@
         <v>62</v>
       </c>
       <c r="P167">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q167">
         <v>3583.62</v>
@@ -21270,7 +21270,7 @@
         <v>69</v>
       </c>
       <c r="P168">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q168">
         <v>17672.4</v>
@@ -21386,7 +21386,7 @@
         <v>46</v>
       </c>
       <c r="P169">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q169">
         <v>2699.9</v>
@@ -21502,7 +21502,7 @@
         <v>54</v>
       </c>
       <c r="P170">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q170">
         <v>1791.22</v>
@@ -21618,7 +21618,7 @@
         <v>14</v>
       </c>
       <c r="P171">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="Q171">
         <v>3481.62</v>
@@ -21734,7 +21734,7 @@
         <v>64</v>
       </c>
       <c r="P172">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q172">
         <v>54.42</v>
@@ -21850,7 +21850,7 @@
         <v>7</v>
       </c>
       <c r="P173">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="Q173">
         <v>244.71</v>
@@ -22180,7 +22180,7 @@
         <v>43</v>
       </c>
       <c r="P176">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q176">
         <v>1106.16</v>
@@ -22528,7 +22528,7 @@
         <v>43</v>
       </c>
       <c r="P179">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q179">
         <v>396.28</v>
@@ -22644,7 +22644,7 @@
         <v>72</v>
       </c>
       <c r="P180">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="Q180">
         <v>196.96</v>
@@ -22760,7 +22760,7 @@
         <v>5</v>
       </c>
       <c r="P181">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q181">
         <v>2150.66</v>
@@ -22876,7 +22876,7 @@
         <v>52</v>
       </c>
       <c r="P182">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q182">
         <v>1472.08</v>
@@ -22992,7 +22992,7 @@
         <v>77</v>
       </c>
       <c r="P183">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q183">
         <v>3068.2</v>
@@ -23438,7 +23438,7 @@
         <v>86</v>
       </c>
       <c r="P187">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="Q187">
         <v>4498.08</v>
@@ -23554,7 +23554,7 @@
         <v>9</v>
       </c>
       <c r="P188">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q188">
         <v>2740.03</v>
@@ -23670,7 +23670,7 @@
         <v>60</v>
       </c>
       <c r="P189">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q189">
         <v>3322.14</v>
@@ -23786,7 +23786,7 @@
         <v>38</v>
       </c>
       <c r="P190">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="Q190">
         <v>10903.8</v>
@@ -24018,7 +24018,7 @@
         <v>19</v>
       </c>
       <c r="P192">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q192">
         <v>1257.16</v>
@@ -24134,7 +24134,7 @@
         <v>36</v>
       </c>
       <c r="P193">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q193">
         <v>613.64</v>
@@ -24250,7 +24250,7 @@
         <v>78</v>
       </c>
       <c r="P194">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q194">
         <v>524.05</v>
@@ -24366,7 +24366,7 @@
         <v>2</v>
       </c>
       <c r="P195">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Q195">
         <v>304.87</v>
@@ -24482,7 +24482,7 @@
         <v>52</v>
       </c>
       <c r="P196">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q196">
         <v>118.37</v>
@@ -24598,7 +24598,7 @@
         <v>31</v>
       </c>
       <c r="P197">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q197">
         <v>1283.44</v>
@@ -24714,7 +24714,7 @@
         <v>68</v>
       </c>
       <c r="P198">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q198">
         <v>3021.42</v>
@@ -24830,7 +24830,7 @@
         <v>10</v>
       </c>
       <c r="P199">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q199">
         <v>179.97</v>
@@ -25062,7 +25062,7 @@
         <v>81</v>
       </c>
       <c r="P201">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q201">
         <v>1100.42</v>

--- a/NIFTY_200_Technical_Metrics.xlsx
+++ b/NIFTY_200_Technical_Metrics.xlsx
@@ -2092,7 +2092,7 @@
         <v>58</v>
       </c>
       <c r="P2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Q2">
         <v>1068.56</v>
@@ -2324,7 +2324,7 @@
         <v>90</v>
       </c>
       <c r="P4">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q4">
         <v>346.55</v>
@@ -2440,7 +2440,7 @@
         <v>96</v>
       </c>
       <c r="P5">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q5">
         <v>1528.3</v>
@@ -2556,7 +2556,7 @@
         <v>91</v>
       </c>
       <c r="P6">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="Q6">
         <v>2941.23</v>
@@ -2672,7 +2672,7 @@
         <v>96</v>
       </c>
       <c r="P7">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="Q7">
         <v>1489.64</v>
@@ -2788,7 +2788,7 @@
         <v>87</v>
       </c>
       <c r="P8">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Q8">
         <v>1804.44</v>
@@ -2904,7 +2904,7 @@
         <v>98</v>
       </c>
       <c r="P9">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q9">
         <v>222.23</v>
@@ -3020,7 +3020,7 @@
         <v>51</v>
       </c>
       <c r="P10">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="Q10">
         <v>5322.2</v>
@@ -3136,7 +3136,7 @@
         <v>14</v>
       </c>
       <c r="P11">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q11">
         <v>412.43</v>
@@ -3252,7 +3252,7 @@
         <v>29</v>
       </c>
       <c r="P12">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q12">
         <v>1792.16</v>
@@ -3368,7 +3368,7 @@
         <v>79</v>
       </c>
       <c r="P13">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q13">
         <v>8472.4</v>
@@ -3484,7 +3484,7 @@
         <v>61</v>
       </c>
       <c r="P14">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q14">
         <v>143.48</v>
@@ -3600,7 +3600,7 @@
         <v>85</v>
       </c>
       <c r="P15">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="Q15">
         <v>2704.14</v>
@@ -3716,7 +3716,7 @@
         <v>28</v>
       </c>
       <c r="P16">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="Q16">
         <v>1507.5</v>
@@ -3832,7 +3832,7 @@
         <v>83</v>
       </c>
       <c r="P17">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q17">
         <v>731.6799999999999</v>
@@ -3948,7 +3948,7 @@
         <v>83</v>
       </c>
       <c r="P18">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q18">
         <v>975.08</v>
@@ -4180,7 +4180,7 @@
         <v>69</v>
       </c>
       <c r="P20">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q20">
         <v>1309.72</v>
@@ -4412,7 +4412,7 @@
         <v>21</v>
       </c>
       <c r="P22">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q22">
         <v>1673.22</v>
@@ -4528,7 +4528,7 @@
         <v>17</v>
       </c>
       <c r="P23">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q23">
         <v>10036</v>
@@ -4644,7 +4644,7 @@
         <v>47</v>
       </c>
       <c r="P24">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q24">
         <v>886.1900000000001</v>
@@ -4760,7 +4760,7 @@
         <v>63</v>
       </c>
       <c r="P25">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q25">
         <v>268.93</v>
@@ -4992,7 +4992,7 @@
         <v>4</v>
       </c>
       <c r="P27">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>1186.82</v>
@@ -5108,7 +5108,7 @@
         <v>35</v>
       </c>
       <c r="P28">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q28">
         <v>408.43</v>
@@ -5224,7 +5224,7 @@
         <v>87</v>
       </c>
       <c r="P29">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q29">
         <v>1931.14</v>
@@ -5340,7 +5340,7 @@
         <v>44</v>
       </c>
       <c r="P30">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q30">
         <v>1798.52</v>
@@ -5456,7 +5456,7 @@
         <v>95</v>
       </c>
       <c r="P31">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Q31">
         <v>381.91</v>
@@ -5688,7 +5688,7 @@
         <v>24</v>
       </c>
       <c r="P33">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q33">
         <v>1569.06</v>
@@ -5804,7 +5804,7 @@
         <v>86</v>
       </c>
       <c r="P34">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="Q34">
         <v>37769</v>
@@ -5920,7 +5920,7 @@
         <v>40</v>
       </c>
       <c r="P35">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q35">
         <v>290.19</v>
@@ -6036,7 +6036,7 @@
         <v>22</v>
       </c>
       <c r="P36">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="Q36">
         <v>5127.1</v>
@@ -6152,7 +6152,7 @@
         <v>93</v>
       </c>
       <c r="P37">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="Q37">
         <v>3954.4</v>
@@ -6268,7 +6268,7 @@
         <v>65</v>
       </c>
       <c r="P38">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q38">
         <v>129.8</v>
@@ -6500,7 +6500,7 @@
         <v>42</v>
       </c>
       <c r="P40">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q40">
         <v>1489.4</v>
@@ -6616,7 +6616,7 @@
         <v>45</v>
       </c>
       <c r="P41">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="Q41">
         <v>1382.82</v>
@@ -6732,7 +6732,7 @@
         <v>64</v>
       </c>
       <c r="P42">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Q42">
         <v>454.5</v>
@@ -6848,7 +6848,7 @@
         <v>5</v>
       </c>
       <c r="P43">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Q43">
         <v>1412.92</v>
@@ -6964,7 +6964,7 @@
         <v>53</v>
       </c>
       <c r="P44">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q44">
         <v>1399.36</v>
@@ -7080,7 +7080,7 @@
         <v>30</v>
       </c>
       <c r="P45">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q45">
         <v>2038.56</v>
@@ -7312,7 +7312,7 @@
         <v>21</v>
       </c>
       <c r="P47">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q47">
         <v>1844.24</v>
@@ -7428,7 +7428,7 @@
         <v>94</v>
       </c>
       <c r="P48">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q48">
         <v>5604.8</v>
@@ -7544,7 +7544,7 @@
         <v>20</v>
       </c>
       <c r="P49">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q49">
         <v>424.38</v>
@@ -7776,7 +7776,7 @@
         <v>31</v>
       </c>
       <c r="P51">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="Q51">
         <v>11481.4</v>
@@ -7892,7 +7892,7 @@
         <v>17</v>
       </c>
       <c r="P52">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q52">
         <v>569.9400000000001</v>
@@ -8124,7 +8124,7 @@
         <v>36</v>
       </c>
       <c r="P54">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q54">
         <v>1273.44</v>
@@ -8466,7 +8466,7 @@
         <v>53</v>
       </c>
       <c r="P57">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q57">
         <v>242.55</v>
@@ -8582,7 +8582,7 @@
         <v>75</v>
       </c>
       <c r="P58">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Q58">
         <v>388.56</v>
@@ -8698,7 +8698,7 @@
         <v>92</v>
       </c>
       <c r="P59">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q59">
         <v>311.25</v>
@@ -8814,7 +8814,7 @@
         <v>82</v>
       </c>
       <c r="P60">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="Q60">
         <v>989.4400000000001</v>
@@ -8930,7 +8930,7 @@
         <v>57</v>
       </c>
       <c r="P61">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="Q61">
         <v>168.16</v>
@@ -9046,7 +9046,7 @@
         <v>73</v>
       </c>
       <c r="P62">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q62">
         <v>2169.76</v>
@@ -9278,7 +9278,7 @@
         <v>32</v>
       </c>
       <c r="P64">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q64">
         <v>2235.18</v>
@@ -9394,7 +9394,7 @@
         <v>26</v>
       </c>
       <c r="P65">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="Q65">
         <v>1016</v>
@@ -9626,7 +9626,7 @@
         <v>79</v>
       </c>
       <c r="P67">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q67">
         <v>3082.36</v>
@@ -9956,7 +9956,7 @@
         <v>29</v>
       </c>
       <c r="P70">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q70">
         <v>4217.12</v>
@@ -10072,7 +10072,7 @@
         <v>7</v>
       </c>
       <c r="P71">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Q71">
         <v>1145.88</v>
@@ -10188,7 +10188,7 @@
         <v>6</v>
       </c>
       <c r="P72">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q72">
         <v>1129.9</v>
@@ -10304,7 +10304,7 @@
         <v>40</v>
       </c>
       <c r="P73">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q73">
         <v>2449.96</v>
@@ -10536,7 +10536,7 @@
         <v>6</v>
       </c>
       <c r="P75">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q75">
         <v>555.0599999999999</v>
@@ -10652,7 +10652,7 @@
         <v>56</v>
       </c>
       <c r="P76">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q76">
         <v>4857.28</v>
@@ -10768,7 +10768,7 @@
         <v>90</v>
       </c>
       <c r="P77">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Q77">
         <v>1044.86</v>
@@ -10884,7 +10884,7 @@
         <v>48</v>
       </c>
       <c r="P78">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q78">
         <v>376.75</v>
@@ -11232,7 +11232,7 @@
         <v>44</v>
       </c>
       <c r="P81">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q81">
         <v>205.53</v>
@@ -11348,7 +11348,7 @@
         <v>55</v>
       </c>
       <c r="P82">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q82">
         <v>1922.9</v>
@@ -11562,7 +11562,7 @@
         <v>48</v>
       </c>
       <c r="P84">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q84">
         <v>1295.26</v>
@@ -11678,7 +11678,7 @@
         <v>18</v>
       </c>
       <c r="P85">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Q85">
         <v>1731.28</v>
@@ -11794,7 +11794,7 @@
         <v>99</v>
       </c>
       <c r="P86">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Q86">
         <v>14.3</v>
@@ -11910,7 +11910,7 @@
         <v>72</v>
       </c>
       <c r="P87">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q87">
         <v>73.51000000000001</v>
@@ -12026,7 +12026,7 @@
         <v>46</v>
       </c>
       <c r="P88">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q88">
         <v>663.99</v>
@@ -12142,7 +12142,7 @@
         <v>76</v>
       </c>
       <c r="P89">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q89">
         <v>837.34</v>
@@ -12258,7 +12258,7 @@
         <v>41</v>
       </c>
       <c r="P90">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q90">
         <v>4526.86</v>
@@ -12374,7 +12374,7 @@
         <v>63</v>
       </c>
       <c r="P91">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q91">
         <v>901.62</v>
@@ -12490,7 +12490,7 @@
         <v>50</v>
       </c>
       <c r="P92">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="Q92">
         <v>418.58</v>
@@ -12606,7 +12606,7 @@
         <v>13</v>
       </c>
       <c r="P93">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q93">
         <v>1138.81</v>
@@ -12722,7 +12722,7 @@
         <v>39</v>
       </c>
       <c r="P94">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Q94">
         <v>137.16</v>
@@ -13070,7 +13070,7 @@
         <v>10</v>
       </c>
       <c r="P97">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q97">
         <v>94.95</v>
@@ -13186,7 +13186,7 @@
         <v>12</v>
       </c>
       <c r="P98">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q98">
         <v>282.12</v>
@@ -13302,7 +13302,7 @@
         <v>58</v>
       </c>
       <c r="P99">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q99">
         <v>1139.42</v>
@@ -13418,7 +13418,7 @@
         <v>22</v>
       </c>
       <c r="P100">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q100">
         <v>231.43</v>
@@ -13534,7 +13534,7 @@
         <v>71</v>
       </c>
       <c r="P101">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="Q101">
         <v>562.72</v>
@@ -13650,7 +13650,7 @@
         <v>80</v>
       </c>
       <c r="P102">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q102">
         <v>1274.42</v>
@@ -13766,7 +13766,7 @@
         <v>3</v>
       </c>
       <c r="P103">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q103">
         <v>419.08</v>
@@ -13882,7 +13882,7 @@
         <v>4</v>
       </c>
       <c r="P104">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q104">
         <v>344.7</v>
@@ -13998,7 +13998,7 @@
         <v>92</v>
       </c>
       <c r="P105">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q105">
         <v>5229.3</v>
@@ -14114,7 +14114,7 @@
         <v>49</v>
       </c>
       <c r="P106">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q106">
         <v>388.71</v>
@@ -14658,7 +14658,7 @@
         <v>49</v>
       </c>
       <c r="P111">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q111">
         <v>546.03</v>
@@ -14774,7 +14774,7 @@
         <v>12</v>
       </c>
       <c r="P112">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q112">
         <v>877.63</v>
@@ -15006,7 +15006,7 @@
         <v>84</v>
       </c>
       <c r="P114">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q114">
         <v>264.09</v>
@@ -15122,7 +15122,7 @@
         <v>13</v>
       </c>
       <c r="P115">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q115">
         <v>3918.26</v>
@@ -15238,7 +15238,7 @@
         <v>62</v>
       </c>
       <c r="P116">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="Q116">
         <v>2266.5</v>
@@ -15354,7 +15354,7 @@
         <v>37</v>
       </c>
       <c r="P117">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q117">
         <v>2990.48</v>
@@ -15470,7 +15470,7 @@
         <v>27</v>
       </c>
       <c r="P118">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q118">
         <v>281.95</v>
@@ -15702,7 +15702,7 @@
         <v>71</v>
       </c>
       <c r="P120">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q120">
         <v>814.39</v>
@@ -15818,7 +15818,7 @@
         <v>56</v>
       </c>
       <c r="P121">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="Q121">
         <v>13113.8</v>
@@ -15934,7 +15934,7 @@
         <v>25</v>
       </c>
       <c r="P122">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="Q122">
         <v>1008.54</v>
@@ -16166,7 +16166,7 @@
         <v>93</v>
       </c>
       <c r="P124">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q124">
         <v>2804.84</v>
@@ -16282,7 +16282,7 @@
         <v>38</v>
       </c>
       <c r="P125">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q125">
         <v>1582.2</v>
@@ -16514,7 +16514,7 @@
         <v>74</v>
       </c>
       <c r="P127">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="Q127">
         <v>849.3</v>
@@ -16630,7 +16630,7 @@
         <v>42</v>
       </c>
       <c r="P128">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q128">
         <v>2304.12</v>
@@ -16746,7 +16746,7 @@
         <v>27</v>
       </c>
       <c r="P129">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q129">
         <v>123323</v>
@@ -16862,7 +16862,7 @@
         <v>59</v>
       </c>
       <c r="P130">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q130">
         <v>2957.36</v>
@@ -16978,7 +16978,7 @@
         <v>95</v>
       </c>
       <c r="P131">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q131">
         <v>377.14</v>
@@ -17094,7 +17094,7 @@
         <v>15</v>
       </c>
       <c r="P132">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="Q132">
         <v>977.8099999999999</v>
@@ -17210,7 +17210,7 @@
         <v>70</v>
       </c>
       <c r="P133">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q133">
         <v>1409.16</v>
@@ -17326,7 +17326,7 @@
         <v>24</v>
       </c>
       <c r="P134">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q134">
         <v>73.22</v>
@@ -17442,7 +17442,7 @@
         <v>82</v>
       </c>
       <c r="P135">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q135">
         <v>89.5</v>
@@ -17674,7 +17674,7 @@
         <v>84</v>
       </c>
       <c r="P137">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q137">
         <v>264.7</v>
@@ -17906,7 +17906,7 @@
         <v>85</v>
       </c>
       <c r="P139">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q139">
         <v>9491.700000000001</v>
@@ -18022,7 +18022,7 @@
         <v>20</v>
       </c>
       <c r="P140">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q140">
         <v>446.29</v>
@@ -18138,7 +18138,7 @@
         <v>32</v>
       </c>
       <c r="P141">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q141">
         <v>254.87</v>
@@ -18254,7 +18254,7 @@
         <v>59</v>
       </c>
       <c r="P142">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q142">
         <v>38355</v>
@@ -18370,7 +18370,7 @@
         <v>8</v>
       </c>
       <c r="P143">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q143">
         <v>421.25</v>
@@ -18602,7 +18602,7 @@
         <v>30</v>
       </c>
       <c r="P145">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="Q145">
         <v>4939.2</v>
@@ -18718,7 +18718,7 @@
         <v>50</v>
       </c>
       <c r="P146">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q146">
         <v>425.98</v>
@@ -18950,7 +18950,7 @@
         <v>60</v>
       </c>
       <c r="P148">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q148">
         <v>1496.48</v>
@@ -19066,7 +19066,7 @@
         <v>11</v>
       </c>
       <c r="P149">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="Q149">
         <v>2799.56</v>
@@ -19182,7 +19182,7 @@
         <v>45</v>
       </c>
       <c r="P150">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="Q150">
         <v>104.69</v>
@@ -19298,7 +19298,7 @@
         <v>28</v>
       </c>
       <c r="P151">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q151">
         <v>1514.16</v>
@@ -19414,7 +19414,7 @@
         <v>94</v>
       </c>
       <c r="P152">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q152">
         <v>9512</v>
@@ -19762,7 +19762,7 @@
         <v>76</v>
       </c>
       <c r="P155">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q155">
         <v>1067.14</v>
@@ -19878,7 +19878,7 @@
         <v>34</v>
       </c>
       <c r="P156">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q156">
         <v>1344.44</v>
@@ -20110,7 +20110,7 @@
         <v>35</v>
       </c>
       <c r="P158">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q158">
         <v>345.84</v>
@@ -20226,7 +20226,7 @@
         <v>25</v>
       </c>
       <c r="P159">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q159">
         <v>1269.46</v>
@@ -20342,7 +20342,7 @@
         <v>2</v>
       </c>
       <c r="P160">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q160">
         <v>229.15</v>
@@ -20458,7 +20458,7 @@
         <v>88</v>
       </c>
       <c r="P161">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q161">
         <v>183.39</v>
@@ -20574,7 +20574,7 @@
         <v>3</v>
       </c>
       <c r="P162">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q162">
         <v>579.58</v>
@@ -20690,7 +20690,7 @@
         <v>23</v>
       </c>
       <c r="P163">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q163">
         <v>1737.46</v>
@@ -20806,7 +20806,7 @@
         <v>70</v>
       </c>
       <c r="P164">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q164">
         <v>1001.15</v>
@@ -21038,7 +21038,7 @@
         <v>77</v>
       </c>
       <c r="P166">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q166">
         <v>909.38</v>
@@ -21154,7 +21154,7 @@
         <v>62</v>
       </c>
       <c r="P167">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q167">
         <v>3583.62</v>
@@ -21270,7 +21270,7 @@
         <v>69</v>
       </c>
       <c r="P168">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="Q168">
         <v>17672.4</v>
@@ -21386,7 +21386,7 @@
         <v>46</v>
       </c>
       <c r="P169">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q169">
         <v>2699.9</v>
@@ -21502,7 +21502,7 @@
         <v>54</v>
       </c>
       <c r="P170">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q170">
         <v>1791.22</v>
@@ -21618,7 +21618,7 @@
         <v>14</v>
       </c>
       <c r="P171">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q171">
         <v>3481.62</v>
@@ -21850,7 +21850,7 @@
         <v>7</v>
       </c>
       <c r="P173">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q173">
         <v>244.71</v>
@@ -22064,7 +22064,7 @@
         <v>88</v>
       </c>
       <c r="P175">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="Q175">
         <v>1958.56</v>
@@ -22180,7 +22180,7 @@
         <v>43</v>
       </c>
       <c r="P176">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q176">
         <v>1106.16</v>
@@ -22296,7 +22296,7 @@
         <v>8</v>
       </c>
       <c r="P177">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q177">
         <v>4105.77</v>
@@ -22412,7 +22412,7 @@
         <v>54</v>
       </c>
       <c r="P178">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q178">
         <v>651.13</v>
@@ -22528,7 +22528,7 @@
         <v>43</v>
       </c>
       <c r="P179">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q179">
         <v>396.28</v>
@@ -22644,7 +22644,7 @@
         <v>72</v>
       </c>
       <c r="P180">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q180">
         <v>196.96</v>
@@ -22760,7 +22760,7 @@
         <v>5</v>
       </c>
       <c r="P181">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="Q181">
         <v>2150.66</v>
@@ -22876,7 +22876,7 @@
         <v>52</v>
       </c>
       <c r="P182">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="Q182">
         <v>1472.08</v>
@@ -22992,7 +22992,7 @@
         <v>77</v>
       </c>
       <c r="P183">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q183">
         <v>3068.2</v>
@@ -23322,7 +23322,7 @@
         <v>23</v>
       </c>
       <c r="P186">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q186">
         <v>384.74</v>
@@ -23438,7 +23438,7 @@
         <v>86</v>
       </c>
       <c r="P187">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q187">
         <v>4498.08</v>
@@ -23554,7 +23554,7 @@
         <v>9</v>
       </c>
       <c r="P188">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q188">
         <v>2740.03</v>
@@ -23786,7 +23786,7 @@
         <v>38</v>
       </c>
       <c r="P190">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q190">
         <v>10903.8</v>
@@ -23902,7 +23902,7 @@
         <v>57</v>
       </c>
       <c r="P191">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q191">
         <v>167.33</v>
@@ -24018,7 +24018,7 @@
         <v>19</v>
       </c>
       <c r="P192">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q192">
         <v>1257.16</v>
@@ -24134,7 +24134,7 @@
         <v>36</v>
       </c>
       <c r="P193">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q193">
         <v>613.64</v>
@@ -24366,7 +24366,7 @@
         <v>2</v>
       </c>
       <c r="P195">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q195">
         <v>304.87</v>
@@ -24482,7 +24482,7 @@
         <v>52</v>
       </c>
       <c r="P196">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q196">
         <v>118.37</v>
@@ -24598,7 +24598,7 @@
         <v>31</v>
       </c>
       <c r="P197">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q197">
         <v>1283.44</v>
@@ -24714,7 +24714,7 @@
         <v>68</v>
       </c>
       <c r="P198">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Q198">
         <v>3021.42</v>
@@ -24830,7 +24830,7 @@
         <v>10</v>
       </c>
       <c r="P199">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q199">
         <v>179.97</v>
@@ -24946,7 +24946,7 @@
         <v>73</v>
       </c>
       <c r="P200">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q200">
         <v>22.84</v>
